--- a/sports_forms/030_gracie_barra_exit_plan_template--sports_forms.xlsx
+++ b/sports_forms/030_gracie_barra_exit_plan_template--sports_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -883,7 +883,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>first name</t>
+          <t>Form 2 First Name</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,7 +906,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>last name</t>
+          <t>Form 2 Last Name</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,7 +929,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Form 2 Email</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Form 2 Phone</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -975,7 +975,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Form 2 Date</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>Form 2 Note</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>first time</t>
+          <t>Form 2 First Time</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>second time</t>
+          <t>Form 2 Second Time</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>third time</t>
+          <t>Form 2 Third Time</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
